--- a/RMUTL_WORK/Teaching work/2025/เทอม_02/ENGCE121_Computer Architecture and Organization/SCORE_121.xlsx
+++ b/RMUTL_WORK/Teaching work/2025/เทอม_02/ENGCE121_Computer Architecture and Organization/SCORE_121.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LOBSTER69\Documents\GitHub\WORK\RMUTL_WORK\Teaching work\2025\เทอม_02\ENGCE121_Computer Architecture and Organization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3AF02BC-3E75-46B8-A1B8-3B5E6F90CB44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39D7DF63-65D4-4EE5-89C3-C2DA6E069B53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -261,12 +261,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -274,6 +268,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -604,157 +604,157 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.8">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
-      <c r="Q1" s="7"/>
-      <c r="R1" s="7"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="10"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.8">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.8">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
-      <c r="P3" s="7"/>
-      <c r="Q3" s="7"/>
-      <c r="R3" s="7"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="10"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.8">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
-      <c r="O4" s="7"/>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="7"/>
-      <c r="R4" s="7"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="10"/>
+      <c r="R4" s="10"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.8">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8" t="s">
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
-      <c r="M5" s="8"/>
-      <c r="N5" s="8" t="s">
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="O5" s="8" t="s">
+      <c r="O5" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="P5" s="8" t="s">
+      <c r="P5" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="Q5" s="8" t="s">
+      <c r="Q5" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="R5" s="8" t="s">
+      <c r="R5" s="11" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.8">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
-      <c r="M6" s="8"/>
-      <c r="N6" s="8"/>
-      <c r="O6" s="8"/>
-      <c r="P6" s="8"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="8"/>
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="11"/>
+      <c r="O6" s="11"/>
+      <c r="P6" s="11"/>
+      <c r="Q6" s="11"/>
+      <c r="R6" s="11"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.8">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
+      <c r="A7" s="11"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
       <c r="D7" s="3" t="s">
         <v>12</v>
       </c>
@@ -785,11 +785,11 @@
       <c r="M7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8"/>
-      <c r="P7" s="8"/>
-      <c r="Q7" s="8"/>
-      <c r="R7" s="8"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="11"/>
+      <c r="P7" s="11"/>
+      <c r="Q7" s="11"/>
+      <c r="R7" s="11"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.8">
       <c r="A8" s="6">
@@ -801,10 +801,10 @@
       <c r="C8" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="7">
         <v>10</v>
       </c>
-      <c r="E8" s="10"/>
+      <c r="E8" s="8"/>
       <c r="F8" s="2">
         <v>3.6</v>
       </c>
@@ -814,20 +814,22 @@
       <c r="H8" s="2">
         <v>5</v>
       </c>
-      <c r="I8" s="11">
+      <c r="I8" s="9">
         <v>10</v>
       </c>
-      <c r="J8" s="10"/>
+      <c r="J8" s="8"/>
       <c r="K8" s="2">
         <v>3.8</v>
       </c>
-      <c r="L8" s="2"/>
+      <c r="L8" s="2">
+        <v>6.5</v>
+      </c>
       <c r="M8" s="2">
         <v>5</v>
       </c>
       <c r="N8" s="2">
         <f>SUM(D8:M8)</f>
-        <v>40.6</v>
+        <v>47.1</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" s="2"/>
@@ -844,10 +846,10 @@
       <c r="C9" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="7">
         <v>10</v>
       </c>
-      <c r="E9" s="10"/>
+      <c r="E9" s="8"/>
       <c r="F9" s="2">
         <v>3.3</v>
       </c>
@@ -857,20 +859,22 @@
       <c r="H9" s="2">
         <v>5</v>
       </c>
-      <c r="I9" s="11">
+      <c r="I9" s="9">
         <v>10</v>
       </c>
-      <c r="J9" s="10"/>
+      <c r="J9" s="8"/>
       <c r="K9" s="2">
         <v>4.5999999999999996</v>
       </c>
-      <c r="L9" s="2"/>
+      <c r="L9" s="2">
+        <v>10</v>
+      </c>
       <c r="M9" s="2">
         <v>5</v>
       </c>
       <c r="N9" s="2">
         <f>SUM(D9:M9)</f>
-        <v>46.1</v>
+        <v>56.1</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" s="2"/>
@@ -887,10 +891,10 @@
       <c r="C10" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="7">
         <v>10</v>
       </c>
-      <c r="E10" s="10"/>
+      <c r="E10" s="8"/>
       <c r="F10" s="2">
         <v>5.4</v>
       </c>
@@ -900,20 +904,22 @@
       <c r="H10" s="2">
         <v>3</v>
       </c>
-      <c r="I10" s="11">
+      <c r="I10" s="9">
         <v>10</v>
       </c>
-      <c r="J10" s="10"/>
+      <c r="J10" s="8"/>
       <c r="K10" s="2">
         <v>3.4</v>
       </c>
-      <c r="L10" s="2"/>
+      <c r="L10" s="2">
+        <v>8</v>
+      </c>
       <c r="M10" s="2">
         <v>5</v>
       </c>
       <c r="N10" s="2">
         <f>SUM(D10:M10)</f>
-        <v>45.75</v>
+        <v>53.75</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" s="2"/>
@@ -926,7 +932,7 @@
       </c>
       <c r="N11" s="5">
         <f>AVERAGE(N8:N10)</f>
-        <v>44.15</v>
+        <v>52.316666666666663</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.8">
@@ -935,18 +941,12 @@
       </c>
       <c r="N12" s="2">
         <f>_xlfn.STDEV.P(N8:N10)</f>
-        <v>2.5142924783458795</v>
+        <v>3.8114593297347699</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="20">
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="I10:J10"/>
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="A2:R2"/>
     <mergeCell ref="A3:R3"/>
@@ -961,6 +961,12 @@
     <mergeCell ref="C5:C7"/>
     <mergeCell ref="D5:H6"/>
     <mergeCell ref="I5:M6"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="I10:J10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/RMUTL_WORK/Teaching work/2025/เทอม_02/ENGCE121_Computer Architecture and Organization/SCORE_121.xlsx
+++ b/RMUTL_WORK/Teaching work/2025/เทอม_02/ENGCE121_Computer Architecture and Organization/SCORE_121.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LOBSTER69\Documents\GitHub\WORK\RMUTL_WORK\Teaching work\2025\เทอม_02\ENGCE121_Computer Architecture and Organization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39D7DF63-65D4-4EE5-89C3-C2DA6E069B53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{679832E6-024D-415E-9984-D0EAD0B784E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
   <si>
     <t>มหาวิทยาลัยเทคโนโลยีราชมงคลล้านนา เชียงราย</t>
   </si>
@@ -121,7 +121,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -142,6 +142,14 @@
       <family val="2"/>
       <charset val="222"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFF0000"/>
+      <name val="TH SarabunPSK"/>
+      <family val="2"/>
+      <charset val="222"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -151,7 +159,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -169,19 +177,6 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -254,26 +249,26 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -580,7 +575,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R12"/>
+  <dimension ref="A1:R10"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="24" x14ac:dyDescent="0.8"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -604,157 +599,157 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.8">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
-      <c r="O1" s="10"/>
-      <c r="P1" s="10"/>
-      <c r="Q1" s="10"/>
-      <c r="R1" s="10"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
+      <c r="Q1" s="6"/>
+      <c r="R1" s="6"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.8">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="10"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.8">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
-      <c r="N3" s="10"/>
-      <c r="O3" s="10"/>
-      <c r="P3" s="10"/>
-      <c r="Q3" s="10"/>
-      <c r="R3" s="10"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.8">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
-      <c r="N4" s="10"/>
-      <c r="O4" s="10"/>
-      <c r="P4" s="10"/>
-      <c r="Q4" s="10"/>
-      <c r="R4" s="10"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.8">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11" t="s">
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11"/>
-      <c r="N5" s="11" t="s">
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="O5" s="11" t="s">
+      <c r="O5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="P5" s="11" t="s">
+      <c r="P5" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="Q5" s="11" t="s">
+      <c r="Q5" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="R5" s="11" t="s">
+      <c r="R5" s="7" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.8">
-      <c r="A6" s="11"/>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11"/>
-      <c r="N6" s="11"/>
-      <c r="O6" s="11"/>
-      <c r="P6" s="11"/>
-      <c r="Q6" s="11"/>
-      <c r="R6" s="11"/>
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7"/>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.8">
-      <c r="A7" s="11"/>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
       <c r="D7" s="3" t="s">
         <v>12</v>
       </c>
@@ -785,26 +780,26 @@
       <c r="M7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="N7" s="11"/>
-      <c r="O7" s="11"/>
-      <c r="P7" s="11"/>
-      <c r="Q7" s="11"/>
-      <c r="R7" s="11"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="7"/>
+      <c r="P7" s="7"/>
+      <c r="Q7" s="7"/>
+      <c r="R7" s="7"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.8">
-      <c r="A8" s="6">
+      <c r="A8" s="4">
         <v>1</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="8">
         <v>10</v>
       </c>
-      <c r="E8" s="8"/>
+      <c r="E8" s="9"/>
       <c r="F8" s="2">
         <v>3.6</v>
       </c>
@@ -814,10 +809,10 @@
       <c r="H8" s="2">
         <v>5</v>
       </c>
-      <c r="I8" s="9">
+      <c r="I8" s="10">
         <v>10</v>
       </c>
-      <c r="J8" s="8"/>
+      <c r="J8" s="11"/>
       <c r="K8" s="2">
         <v>3.8</v>
       </c>
@@ -831,25 +826,37 @@
         <f>SUM(D8:M8)</f>
         <v>47.1</v>
       </c>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="3"/>
+      <c r="O8" s="2">
+        <f>AVERAGE(N8:N10)</f>
+        <v>52.316666666666663</v>
+      </c>
+      <c r="P8" s="2">
+        <f>_xlfn.STDEV.P(N8:N10)</f>
+        <v>3.8114593297347699</v>
+      </c>
+      <c r="Q8" s="2">
+        <f>(N8-O8)/P8</f>
+        <v>-1.3686796094003386</v>
+      </c>
+      <c r="R8" s="3" t="str">
+        <f>IF(N8&gt;=70, "A", IF(N8&gt;=65, "B+", IF(N8&gt;=60, "B", IF(N8&gt;=55, "C+", IF(N8&gt;=50, "C", IF(N8&gt;=45, "D+", IF(N8&gt;=40, "D", "F")))))))</f>
+        <v>D+</v>
+      </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.8">
-      <c r="A9" s="6">
+      <c r="A9" s="4">
         <v>2</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="8">
         <v>10</v>
       </c>
-      <c r="E9" s="8"/>
+      <c r="E9" s="9"/>
       <c r="F9" s="2">
         <v>3.3</v>
       </c>
@@ -859,10 +866,10 @@
       <c r="H9" s="2">
         <v>5</v>
       </c>
-      <c r="I9" s="9">
+      <c r="I9" s="10">
         <v>10</v>
       </c>
-      <c r="J9" s="8"/>
+      <c r="J9" s="11"/>
       <c r="K9" s="2">
         <v>4.5999999999999996</v>
       </c>
@@ -876,25 +883,37 @@
         <f>SUM(D9:M9)</f>
         <v>56.1</v>
       </c>
-      <c r="O9" s="2"/>
-      <c r="P9" s="2"/>
-      <c r="Q9" s="2"/>
-      <c r="R9" s="3"/>
+      <c r="O9" s="2">
+        <f>AVERAGE(N8:N10)</f>
+        <v>52.316666666666663</v>
+      </c>
+      <c r="P9" s="2">
+        <f>_xlfn.STDEV.P(N8:N10)</f>
+        <v>3.8114593297347699</v>
+      </c>
+      <c r="Q9" s="2">
+        <f>(N9-O9)/P9</f>
+        <v>0.99262067518810737</v>
+      </c>
+      <c r="R9" s="5" t="str">
+        <f t="shared" ref="R9:R10" si="0">IF(N9&gt;=70, "A", IF(N9&gt;=65, "B+", IF(N9&gt;=60, "B", IF(N9&gt;=55, "C+", IF(N9&gt;=50, "C", IF(N9&gt;=45, "D+", IF(N9&gt;=40, "D", "F")))))))</f>
+        <v>C+</v>
+      </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.8">
-      <c r="A10" s="6">
+      <c r="A10" s="4">
         <v>3</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="8">
         <v>10</v>
       </c>
-      <c r="E10" s="8"/>
+      <c r="E10" s="9"/>
       <c r="F10" s="2">
         <v>5.4</v>
       </c>
@@ -904,10 +923,10 @@
       <c r="H10" s="2">
         <v>3</v>
       </c>
-      <c r="I10" s="9">
+      <c r="I10" s="10">
         <v>10</v>
       </c>
-      <c r="J10" s="8"/>
+      <c r="J10" s="11"/>
       <c r="K10" s="2">
         <v>3.4</v>
       </c>
@@ -921,32 +940,32 @@
         <f>SUM(D10:M10)</f>
         <v>53.75</v>
       </c>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2"/>
-      <c r="Q10" s="2"/>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.8">
-      <c r="M11" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="N11" s="5">
+      <c r="O10" s="2">
         <f>AVERAGE(N8:N10)</f>
         <v>52.316666666666663</v>
       </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.8">
-      <c r="M12" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="N12" s="2">
+      <c r="P10" s="2">
         <f>_xlfn.STDEV.P(N8:N10)</f>
         <v>3.8114593297347699</v>
+      </c>
+      <c r="Q10" s="2">
+        <f>(N10-O10)/P10</f>
+        <v>0.37605893421223502</v>
+      </c>
+      <c r="R10" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>C</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="20">
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="I10:J10"/>
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="A2:R2"/>
     <mergeCell ref="A3:R3"/>
@@ -961,12 +980,6 @@
     <mergeCell ref="C5:C7"/>
     <mergeCell ref="D5:H6"/>
     <mergeCell ref="I5:M6"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="I10:J10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/RMUTL_WORK/Teaching work/2025/เทอม_02/ENGCE121_Computer Architecture and Organization/SCORE_121.xlsx
+++ b/RMUTL_WORK/Teaching work/2025/เทอม_02/ENGCE121_Computer Architecture and Organization/SCORE_121.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LOBSTER69\Documents\GitHub\WORK\RMUTL_WORK\Teaching work\2025\เทอม_02\ENGCE121_Computer Architecture and Organization\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LOBSTER69\Documents\WORK\RMUTL_WORK\Teaching work\2025\เทอม_02\ENGCE121_Computer Architecture and Organization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{679832E6-024D-415E-9984-D0EAD0B784E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E96D08D2-658C-4F57-8481-48C6BBE45C76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5805" yWindow="2940" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ประวัติการศึกษา" sheetId="1" r:id="rId1"/>
@@ -121,7 +121,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -138,14 +138,6 @@
     <font>
       <b/>
       <sz val="16"/>
-      <name val="TH SarabunPSK"/>
-      <family val="2"/>
-      <charset val="222"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color rgb="FFFF0000"/>
       <name val="TH SarabunPSK"/>
       <family val="2"/>
       <charset val="222"/>
@@ -240,7 +232,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -253,27 +245,24 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
@@ -576,180 +565,180 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R10"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="24" x14ac:dyDescent="0.8"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="24" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="7.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="5" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="8.7265625" style="1"/>
+    <col min="19" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.8">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="8"/>
+      <c r="P1" s="8"/>
+      <c r="Q1" s="8"/>
+      <c r="R1" s="8"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.8">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
+      <c r="N2" s="8"/>
+      <c r="O2" s="8"/>
+      <c r="P2" s="8"/>
+      <c r="Q2" s="8"/>
+      <c r="R2" s="8"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.8">
-      <c r="A3" s="6" t="s">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
+      <c r="O3" s="8"/>
+      <c r="P3" s="8"/>
+      <c r="Q3" s="8"/>
+      <c r="R3" s="8"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.8">
-      <c r="A4" s="6" t="s">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="8"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="8"/>
+      <c r="Q4" s="8"/>
+      <c r="R4" s="8"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.8">
-      <c r="A5" s="7" t="s">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7" t="s">
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7" t="s">
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="O5" s="7" t="s">
+      <c r="O5" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="P5" s="7" t="s">
+      <c r="P5" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="Q5" s="7" t="s">
+      <c r="Q5" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="R5" s="7" t="s">
+      <c r="R5" s="9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.8">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="7"/>
-      <c r="R6" s="7"/>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="9"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
+      <c r="O6" s="9"/>
+      <c r="P6" s="9"/>
+      <c r="Q6" s="9"/>
+      <c r="R6" s="9"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.8">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="9"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
       <c r="D7" s="3" t="s">
         <v>12</v>
       </c>
@@ -780,13 +769,13 @@
       <c r="M7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="N7" s="7"/>
-      <c r="O7" s="7"/>
-      <c r="P7" s="7"/>
-      <c r="Q7" s="7"/>
-      <c r="R7" s="7"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="9"/>
+      <c r="R7" s="9"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.8">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="4">
         <v>1</v>
       </c>
@@ -796,10 +785,10 @@
       <c r="C8" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="6">
         <v>10</v>
       </c>
-      <c r="E8" s="9"/>
+      <c r="E8" s="7"/>
       <c r="F8" s="2">
         <v>3.6</v>
       </c>
@@ -812,7 +801,7 @@
       <c r="I8" s="10">
         <v>10</v>
       </c>
-      <c r="J8" s="11"/>
+      <c r="J8" s="7"/>
       <c r="K8" s="2">
         <v>3.8</v>
       </c>
@@ -843,7 +832,7 @@
         <v>D+</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.8">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="4">
         <v>2</v>
       </c>
@@ -853,10 +842,10 @@
       <c r="C9" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="6">
         <v>10</v>
       </c>
-      <c r="E9" s="9"/>
+      <c r="E9" s="7"/>
       <c r="F9" s="2">
         <v>3.3</v>
       </c>
@@ -869,7 +858,7 @@
       <c r="I9" s="10">
         <v>10</v>
       </c>
-      <c r="J9" s="11"/>
+      <c r="J9" s="7"/>
       <c r="K9" s="2">
         <v>4.5999999999999996</v>
       </c>
@@ -900,7 +889,7 @@
         <v>C+</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.8">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="4">
         <v>3</v>
       </c>
@@ -910,10 +899,10 @@
       <c r="C10" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="6">
         <v>10</v>
       </c>
-      <c r="E10" s="9"/>
+      <c r="E10" s="7"/>
       <c r="F10" s="2">
         <v>5.4</v>
       </c>
@@ -926,7 +915,7 @@
       <c r="I10" s="10">
         <v>10</v>
       </c>
-      <c r="J10" s="11"/>
+      <c r="J10" s="7"/>
       <c r="K10" s="2">
         <v>3.4</v>
       </c>
@@ -960,12 +949,6 @@
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="20">
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="I10:J10"/>
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="A2:R2"/>
     <mergeCell ref="A3:R3"/>
@@ -980,6 +963,12 @@
     <mergeCell ref="C5:C7"/>
     <mergeCell ref="D5:H6"/>
     <mergeCell ref="I5:M6"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="I10:J10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
